--- a/Backend/Input/ADP/Monitoreo ADP - Nivel II.xlsx
+++ b/Backend/Input/ADP/Monitoreo ADP - Nivel II.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/Nivel II/2025/Abril/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ARMM/ADP/Nivel II/2025/Mayo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED97FE8F-3F8D-406C-8010-B7AE46AFB696}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{715492F3-C5AA-4C71-94A3-965FC2734F0A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Servicio</t>
-  </si>
-  <si>
-    <t>Convenio totalmente tramitado</t>
   </si>
   <si>
     <t>Monitoreo Año 1</t>
@@ -68,16 +65,19 @@
     <t xml:space="preserve">SLEP Chiloé </t>
   </si>
   <si>
-    <t>ABRIL</t>
+    <t>Mayo</t>
   </si>
   <si>
     <t>Comentarios</t>
   </si>
   <si>
-    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 1er año de gestión.</t>
+    <t>Se envía solicitud de informe de monitoreo para el segundo año de gestión, el cual debe enviarse a más tardar el 01 de junio de 2025.</t>
   </si>
   <si>
-    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el convenio del Jefe de Planificación y Control de Gestión del SLEP Chiloé. Esto se realizó ante la ausencia de un Director del SLEP nombrado a la fecha del acto administrativo.</t>
+    <t>Se nombra a Director Ejecutivo el 24 de febrero, por lo que no corresponde al Ministro, hacer seguimiento al II nivel, ya que finaliza la subrogancia.</t>
+  </si>
+  <si>
+    <t>Fecha de nombramiento</t>
   </si>
 </sst>
 </file>
@@ -137,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +147,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -169,7 +175,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -181,6 +187,36 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -197,6 +233,36 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -296,53 +362,152 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C29CBF-8F22-456D-B3FB-D5E8EA4BA277}">
-  <dimension ref="B3:I12"/>
+  <dimension ref="B3:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -693,125 +858,121 @@
   <sheetData>
     <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="14">
+      <c r="B5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9">
         <v>45231</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>45413</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="9">
         <v>45597</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="9">
         <v>45778</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="11">
         <v>45962</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <v>46143</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="15">
         <v>46327</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
-        <v>45658</v>
-      </c>
-      <c r="D6" s="3">
-        <v>45809</v>
-      </c>
-      <c r="E6" s="14">
-        <v>46023</v>
-      </c>
-      <c r="F6" s="14">
-        <v>46174</v>
-      </c>
-      <c r="G6" s="14">
-        <v>46388</v>
-      </c>
-      <c r="H6" s="14">
-        <v>46539</v>
-      </c>
-      <c r="I6" s="14">
-        <v>46753</v>
-      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="12"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="9" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="11" t="s">
-        <v>10</v>
+      <c r="C9" s="24" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>11</v>
       </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
     </row>
-    <row r="11" spans="2:9" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
+    <row r="12" spans="2:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="23"/>
     </row>
-    <row r="12" spans="2:9" ht="168.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+    <row r="13" spans="2:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="2:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Backend/Input/ADP/Monitoreo ADP - Nivel II.xlsx
+++ b/Backend/Input/ADP/Monitoreo ADP - Nivel II.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ARMM/ADP/Nivel II/2025/Mayo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ARMM/ADP/Nivel II/2025/Junio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{715492F3-C5AA-4C71-94A3-965FC2734F0A}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="121_{409E5ACD-61F7-473E-971C-C699A3E8623F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FA4F51B-94EA-48E7-B2AE-6361C2BF054D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>Servicio</t>
   </si>
@@ -62,29 +62,41 @@
     <t>SLEP Gabriela Mistral</t>
   </si>
   <si>
-    <t xml:space="preserve">SLEP Chiloé </t>
-  </si>
-  <si>
-    <t>Mayo</t>
-  </si>
-  <si>
     <t>Comentarios</t>
   </si>
   <si>
-    <t>Se envía solicitud de informe de monitoreo para el segundo año de gestión, el cual debe enviarse a más tardar el 01 de junio de 2025.</t>
-  </si>
-  <si>
-    <t>Se nombra a Director Ejecutivo el 24 de febrero, por lo que no corresponde al Ministro, hacer seguimiento al II nivel, ya que finaliza la subrogancia.</t>
-  </si>
-  <si>
     <t>Fecha de nombramiento</t>
+  </si>
+  <si>
+    <t>SLEP  Magallanes</t>
+  </si>
+  <si>
+    <t>SLEP  Costa Araucanía</t>
+  </si>
+  <si>
+    <t>SLEP Chinchorro</t>
+  </si>
+  <si>
+    <t>En junio se realizó el monitoreo del segundo período de la ADP que se encuentra subrogando de manera prolongada al Director Ejecutivo del SLEP. Dicho informe fue enviado por Gabinete de Ministro al ADP, con las observaciones emanadas por parte del DPCG.</t>
+  </si>
+  <si>
+    <t>En junio se realizó el monitoreo del tercer período del ADP que se encuentra subrogando de manera prolongada al Director Ejecutivo del SLEP. Dicho informe fue enviado por Gabinete de Ministro al ADP, con las observaciones emanadas por parte del DPCG.</t>
+  </si>
+  <si>
+    <t>En junio, se comunica a DPCG la activación de la subrogancia prolongada para el ADP II nivel. Se solicitó el respectivo informe de evaluación para el segundo período, el cual debe ser entregado a fines del mes de julio.</t>
+  </si>
+  <si>
+    <t>En junio, se comunica a DPCG la activación de la subrogancia prolongada para el ADP II nivel. Se solicitará el respectivo informe de evaluación para el segundo período, durante el mes de agosto.</t>
+  </si>
+  <si>
+    <t>Junio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,13 +107,6 @@
     <font>
       <sz val="18"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,19 +130,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,30 +151,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF2D0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -337,117 +324,108 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -458,62 +436,114 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF66CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -843,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C29CBF-8F22-456D-B3FB-D5E8EA4BA277}">
-  <dimension ref="B3:I14"/>
+  <dimension ref="B3:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -858,124 +888,190 @@
   <sheetData>
     <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="15">
         <v>45231</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="15">
         <v>45413</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="15">
         <v>45597</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="21">
         <v>45778</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="15">
         <v>45962</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="15">
         <v>46143</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="16">
         <v>46327</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17">
+        <v>44867</v>
+      </c>
+      <c r="D6" s="17">
+        <v>45048</v>
+      </c>
+      <c r="E6" s="17">
+        <v>45232</v>
+      </c>
+      <c r="F6" s="17">
+        <v>45414</v>
+      </c>
+      <c r="G6" s="17">
+        <v>45598</v>
+      </c>
+      <c r="H6" s="22">
+        <v>45779</v>
+      </c>
+      <c r="I6" s="18">
+        <v>45963</v>
+      </c>
     </row>
     <row r="7" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="17">
+        <v>45108</v>
+      </c>
+      <c r="D7" s="17">
+        <v>45292</v>
+      </c>
+      <c r="E7" s="17">
+        <v>45474</v>
+      </c>
+      <c r="F7" s="17">
+        <v>45658</v>
+      </c>
+      <c r="G7" s="22">
+        <v>45839</v>
+      </c>
+      <c r="H7" s="17">
+        <v>46023</v>
+      </c>
+      <c r="I7" s="18">
+        <v>46204</v>
+      </c>
     </row>
-    <row r="9" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="24" t="s">
-        <v>9</v>
+    <row r="8" spans="2:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="19">
+        <v>45150</v>
+      </c>
+      <c r="D8" s="19">
+        <v>45334</v>
+      </c>
+      <c r="E8" s="19">
+        <v>45516</v>
+      </c>
+      <c r="F8" s="19">
+        <v>45700</v>
+      </c>
+      <c r="G8" s="26">
+        <v>45881</v>
+      </c>
+      <c r="H8" s="19">
+        <v>46065</v>
+      </c>
+      <c r="I8" s="20">
+        <v>46246</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
+    <row r="10" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C11" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="169.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="2:9" ht="168.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="C13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="8"/>
     </row>
-    <row r="11" spans="2:9" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="17" t="s">
+    <row r="14" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
+      <c r="C14" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="8"/>
     </row>
-    <row r="12" spans="2:9" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="21" t="s">
+    <row r="15" spans="2:9" ht="132" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-    </row>
-    <row r="13" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-    </row>
-    <row r="14" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
+      <c r="C15" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -991,18 +1087,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -1266,6 +1350,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E56B48B9-8D50-4C8A-A3A8-779F015C9076}">
   <ds:schemaRefs>
@@ -1275,17 +1371,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD7FD21-EF15-47EF-BE64-355A321DA262}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{070F46FF-6A46-467B-9374-33A76BCB1EEF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1302,4 +1387,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD7FD21-EF15-47EF-BE64-355A321DA262}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>